--- a/data/gravel/No22 Drifter Adventure 2025.xlsx
+++ b/data/gravel/No22 Drifter Adventure 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBBB70C7-4800-B74B-A545-1A4C04C52FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39A1AAE-58E6-0340-BA1C-7743EDDDB1FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22980" yWindow="-17700" windowWidth="26100" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="104">
   <si>
     <t>brand</t>
   </si>
@@ -1559,9 +1559,7 @@
       <c r="A44" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="B44" s="1"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="3"/>

--- a/data/gravel/No22 Drifter Adventure 2025.xlsx
+++ b/data/gravel/No22 Drifter Adventure 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39A1AAE-58E6-0340-BA1C-7743EDDDB1FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07A32E6-E5A6-EB49-B0BE-F7D9405D3AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7620" yWindow="580" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -345,6 +345,9 @@
   </si>
   <si>
     <t>Drifter Adventure</t>
+  </si>
+  <si>
+    <t>https://22bicycles.com/cdn/shop/files/DrifterAdventureProfile.jpg?v=1749001300</t>
   </si>
 </sst>
 </file>
@@ -753,6 +756,11 @@
         <v>101</v>
       </c>
     </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>104</v>
+      </c>
+    </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>

--- a/data/gravel/No22 Drifter Adventure 2025.xlsx
+++ b/data/gravel/No22 Drifter Adventure 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F07A32E6-E5A6-EB49-B0BE-F7D9405D3AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F3F3BE-6923-5E4E-B4E3-8B7B785B19DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7620" yWindow="580" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -269,9 +269,6 @@
     <t>a8:i32</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>threaded</t>
   </si>
   <si>
@@ -348,6 +345,15 @@
   </si>
   <si>
     <t>https://22bicycles.com/cdn/shop/files/DrifterAdventureProfile.jpg?v=1749001300</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Johnstown, New York, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -710,7 +716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -721,7 +727,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -729,7 +735,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -753,12 +759,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -782,28 +788,28 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="H8" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="I8" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>87</v>
       </c>
       <c r="J8" s="1"/>
     </row>
@@ -812,7 +818,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C9" s="1">
         <v>505</v>
@@ -842,7 +848,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C10" s="1">
         <v>430</v>
@@ -872,7 +878,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C11" s="1">
         <v>110</v>
@@ -902,7 +908,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C12" s="1">
         <v>75</v>
@@ -932,7 +938,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C13" s="1">
         <v>70</v>
@@ -962,7 +968,7 @@
         <v>76</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C14" s="1">
         <v>584</v>
@@ -992,7 +998,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C15" s="1">
         <v>440</v>
@@ -1022,7 +1028,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C16" s="1">
         <v>80</v>
@@ -1052,7 +1058,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C17" s="1">
         <v>357</v>
@@ -1082,7 +1088,7 @@
         <v>21</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C18" s="1">
         <v>542</v>
@@ -1112,7 +1118,7 @@
         <v>27</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C19" s="1">
         <v>761</v>
@@ -1642,7 +1648,7 @@
         <v>44</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -1688,7 +1694,7 @@
         <v>47</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -1720,7 +1726,7 @@
         <v>49</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
@@ -1998,7 +2004,7 @@
         <v>67</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
@@ -2009,6 +2015,14 @@
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
     </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>104</v>
+      </c>
+      <c r="B73" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/No22 Drifter Adventure 2025.xlsx
+++ b/data/gravel/No22 Drifter Adventure 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F3F3BE-6923-5E4E-B4E3-8B7B785B19DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D012C60F-3748-0C41-BD4E-11A589A408C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -354,6 +354,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -716,7 +734,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1645,11 +1663,9 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>78</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -1661,7 +1677,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>45</v>
+        <v>108</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -1675,11 +1691,9 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B51" s="1">
-        <v>27.2</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="B51" s="1"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -1691,11 +1705,9 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>99</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="B52" s="1"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -1707,11 +1719,9 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B53" s="1">
-        <v>48</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="B53" s="1"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -1723,11 +1733,9 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>98</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -1739,10 +1747,10 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B55" s="1">
-        <v>160</v>
+        <v>44</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
@@ -1755,11 +1763,9 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B56" s="1">
-        <v>160</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B56" s="1"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -1771,9 +1777,11 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B57" s="1"/>
+        <v>46</v>
+      </c>
+      <c r="B57" s="1">
+        <v>27.2</v>
+      </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -1785,10 +1793,10 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
@@ -1801,9 +1809,11 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B59" s="1"/>
+        <v>48</v>
+      </c>
+      <c r="B59" s="1">
+        <v>48</v>
+      </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -1815,9 +1825,11 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B60" s="1"/>
+        <v>49</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -1829,9 +1841,11 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B61" s="1"/>
+        <v>50</v>
+      </c>
+      <c r="B61" s="1">
+        <v>160</v>
+      </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -1843,10 +1857,10 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B62" s="1">
-        <v>2</v>
+        <v>160</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
@@ -1859,7 +1873,7 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -1873,10 +1887,10 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -1889,11 +1903,9 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>74</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -1905,11 +1917,9 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>74</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
@@ -1921,11 +1931,9 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>74</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
@@ -1937,10 +1945,10 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>74</v>
+        <v>57</v>
+      </c>
+      <c r="B68" s="1">
+        <v>2</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -1953,11 +1961,9 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B69" s="1">
-        <v>6499</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -1969,10 +1975,10 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B70" s="1">
-        <v>12111</v>
+        <v>59</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
@@ -1985,7 +1991,7 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>74</v>
@@ -2001,10 +2007,10 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
@@ -2016,10 +2022,106 @@
       <c r="J72" s="1"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
+      <c r="A73" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B75" s="1">
+        <v>6499</v>
+      </c>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B76" s="1">
+        <v>12111</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>104</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>105</v>
       </c>
     </row>

--- a/data/gravel/No22 Drifter Adventure 2025.xlsx
+++ b/data/gravel/No22 Drifter Adventure 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D012C60F-3748-0C41-BD4E-11A589A408C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD7DF1EC-C609-D147-8267-A12A4918B0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -372,6 +372,9 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>optional</t>
   </si>
 </sst>
 </file>
@@ -1905,7 +1908,9 @@
       <c r="A65" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B65" s="1"/>
+      <c r="B65" s="1" t="s">
+        <v>113</v>
+      </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
